--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="493">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -691,7 +691,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VAERSPatient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
@@ -699,9 +699,6 @@
   </si>
   <si>
     <t>The patient who either received or did not receive the immunization.</t>
-  </si>
-  <si>
-    <t>1876: reference from ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1873,7 +1870,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="58.546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4221,22 +4218,22 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>80</v>
@@ -4244,10 +4241,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4270,13 +4267,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4327,7 +4324,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4348,16 +4345,16 @@
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>80</v>
@@ -4365,10 +4362,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4391,16 +4388,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4438,7 +4435,7 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
@@ -4448,7 +4445,7 @@
         <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4469,30 +4466,30 @@
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AP21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>80</v>
@@ -4514,16 +4511,16 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4573,7 +4570,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>91</v>
@@ -4588,33 +4585,33 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AP22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>243</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4637,13 +4634,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4694,7 +4691,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4721,10 +4718,10 @@
         <v>80</v>
       </c>
       <c r="AO23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>80</v>
@@ -4732,10 +4729,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4758,16 +4755,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4817,7 +4814,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4841,13 +4838,13 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>80</v>
@@ -4855,10 +4852,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4884,13 +4881,13 @@
         <v>166</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4919,11 +4916,11 @@
         <v>170</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4940,7 +4937,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4964,13 +4961,13 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>80</v>
@@ -4978,10 +4975,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5004,13 +5001,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5061,7 +5058,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5082,16 +5079,16 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>80</v>
@@ -5099,10 +5096,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5125,13 +5122,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5182,7 +5179,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5206,24 +5203,24 @@
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5341,10 +5338,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5464,10 +5461,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5493,13 +5490,13 @@
         <v>186</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5549,7 +5546,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5558,7 +5555,7 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>103</v>
@@ -5587,10 +5584,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5616,13 +5613,13 @@
         <v>105</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5651,28 +5648,28 @@
         <v>177</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Z31" t="s" s="2">
+      <c r="AA31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5710,10 +5707,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5739,13 +5736,13 @@
         <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5795,7 +5792,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5822,7 +5819,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5833,10 +5830,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5862,13 +5859,13 @@
         <v>186</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5918,7 +5915,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5933,7 +5930,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5956,10 +5953,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5985,10 +5982,10 @@
         <v>186</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6039,7 +6036,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6054,33 +6051,33 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6103,13 +6100,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6160,7 +6157,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6184,10 +6181,10 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6198,10 +6195,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6227,10 +6224,10 @@
         <v>166</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6260,11 +6257,11 @@
         <v>170</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6281,7 +6278,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6296,33 +6293,33 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6348,10 +6345,10 @@
         <v>166</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6381,11 +6378,11 @@
         <v>170</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6402,7 +6399,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6426,24 +6423,24 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6561,10 +6558,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6684,10 +6681,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6809,10 +6806,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6911,7 +6908,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>80</v>
@@ -6934,10 +6931,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6960,13 +6957,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7017,7 +7014,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7041,10 +7038,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7055,10 +7052,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7081,13 +7078,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7138,7 +7135,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7159,13 +7156,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7176,10 +7173,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7297,10 +7294,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7420,14 +7417,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7449,10 +7446,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>140</v>
@@ -7507,7 +7504,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7545,10 +7542,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7574,10 +7571,10 @@
         <v>166</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7607,11 +7604,11 @@
         <v>177</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7628,7 +7625,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7649,13 +7646,13 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7666,10 +7663,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7692,16 +7689,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7751,7 +7748,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -7772,16 +7769,16 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AN48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7789,10 +7786,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7815,13 +7812,13 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7872,7 +7869,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7893,13 +7890,13 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -7910,10 +7907,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7939,10 +7936,10 @@
         <v>166</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7972,11 +7969,11 @@
         <v>170</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7993,7 +7990,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8014,13 +8011,13 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8031,10 +8028,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8057,13 +8054,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8114,7 +8111,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8135,7 +8132,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8152,10 +8149,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8178,23 +8175,23 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>80</v>
@@ -8239,7 +8236,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8263,7 +8260,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8277,10 +8274,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8306,10 +8303,10 @@
         <v>166</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8339,11 +8336,11 @@
         <v>170</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8360,7 +8357,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8398,10 +8395,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8424,13 +8421,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8481,7 +8478,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8493,7 +8490,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8519,10 +8516,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8640,10 +8637,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8763,14 +8760,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8792,10 +8789,10 @@
         <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -8850,7 +8847,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8888,10 +8885,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8917,10 +8914,10 @@
         <v>186</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8971,7 +8968,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8995,7 +8992,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>134</v>
@@ -9009,10 +9006,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9038,10 +9035,10 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9092,7 +9089,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9130,10 +9127,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9156,13 +9153,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9213,7 +9210,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9237,7 +9234,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>134</v>
@@ -9251,10 +9248,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9277,13 +9274,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9334,7 +9331,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9358,7 +9355,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>134</v>
@@ -9372,10 +9369,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9401,10 +9398,10 @@
         <v>166</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9434,11 +9431,11 @@
         <v>170</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>435</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9455,7 +9452,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9479,7 +9476,7 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>134</v>
@@ -9493,10 +9490,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9522,10 +9519,10 @@
         <v>166</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9555,11 +9552,11 @@
         <v>170</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9576,7 +9573,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9614,10 +9611,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9640,16 +9637,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9699,7 +9696,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9723,10 +9720,10 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9737,10 +9734,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9858,10 +9855,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9981,14 +9978,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10010,10 +10007,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>140</v>
@@ -10068,7 +10065,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10106,10 +10103,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10132,13 +10129,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10189,7 +10186,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10213,10 +10210,10 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10227,10 +10224,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10253,13 +10250,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10310,7 +10307,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10334,10 +10331,10 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10348,10 +10345,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10374,13 +10371,13 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10431,7 +10428,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10455,10 +10452,10 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>80</v>
@@ -10469,10 +10466,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10495,13 +10492,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10552,7 +10549,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10590,10 +10587,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10711,10 +10708,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10834,14 +10831,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10863,10 +10860,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -10921,7 +10918,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10959,10 +10956,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10988,10 +10985,10 @@
         <v>186</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11042,7 +11039,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11080,10 +11077,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11106,13 +11103,13 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11163,7 +11160,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11201,10 +11198,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11230,10 +11227,10 @@
         <v>166</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11263,11 +11260,11 @@
         <v>170</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>482</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
       </c>
@@ -11284,7 +11281,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11322,10 +11319,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11348,16 +11345,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11395,7 +11392,7 @@
         <v>80</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
@@ -11405,7 +11402,7 @@
         <v>195</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>91</v>
@@ -11443,13 +11440,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11474,13 +11471,13 @@
         <v>186</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11530,7 +11527,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>91</v>
@@ -11545,7 +11542,7 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>80</v>
@@ -11568,10 +11565,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11594,16 +11591,16 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="N80" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11653,7 +11650,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>VAERS Immunizationvac1</t>
+    <t>VAERS Immunization[vac1]</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="498">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -514,10 +514,16 @@
     <t>Will generally be set to show that the immunization has been completed or not done.  This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
+    <t>completed</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
+  </si>
+  <si>
+    <t>2026: fixed value = #completed</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -551,6 +557,9 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
+    <t>2027: target not supported</t>
+  </si>
+  <si>
     <t>Event.statusReason</t>
   </si>
   <si>
@@ -691,7 +700,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/VAERSPatient)
 </t>
   </si>
   <si>
@@ -699,6 +708,9 @@
   </si>
   <si>
     <t>The patient who either received or did not receive the immunization.</t>
+  </si>
+  <si>
+    <t>1876: reference from ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -815,6 +827,9 @@
   </si>
   <si>
     <t>Reflects the “reliability” of the content.</t>
+  </si>
+  <si>
+    <t>2028: fixed value = false</t>
   </si>
   <si>
     <t>RXA-9</t>
@@ -1870,7 +1885,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="58.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3311,7 +3326,7 @@
         <v>80</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>80</v>
@@ -3326,11 +3341,11 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3363,22 +3378,22 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3386,10 +3401,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3412,16 +3427,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3447,11 +3462,11 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3469,7 +3484,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3484,19 +3499,19 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3507,10 +3522,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3533,13 +3548,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3566,11 +3581,11 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3588,7 +3603,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3597,7 +3612,7 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
@@ -3609,27 +3624,27 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3652,13 +3667,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3709,7 +3724,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3736,7 +3751,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -3747,10 +3762,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3779,7 +3794,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3820,19 +3835,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3859,7 +3874,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3870,10 +3885,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3896,19 +3911,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3957,7 +3972,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3981,10 +3996,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -3995,10 +4010,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4021,19 +4036,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4082,7 +4097,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4097,7 +4112,7 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
@@ -4106,10 +4121,10 @@
         <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4120,14 +4135,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4146,13 +4161,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4203,7 +4218,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>91</v>
@@ -4218,22 +4233,22 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>80</v>
@@ -4241,10 +4256,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4267,13 +4282,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4324,7 +4339,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4345,16 +4360,16 @@
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>80</v>
@@ -4362,10 +4377,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4388,16 +4403,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4435,17 +4450,17 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4466,30 +4481,30 @@
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>80</v>
@@ -4511,16 +4526,16 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4570,7 +4585,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>91</v>
@@ -4585,33 +4600,33 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>242</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4634,13 +4649,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4691,7 +4706,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4718,10 +4733,10 @@
         <v>80</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>80</v>
@@ -4729,10 +4744,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4755,16 +4770,16 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4775,7 +4790,7 @@
         <v>80</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>80</v>
@@ -4814,7 +4829,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4829,7 +4844,7 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>261</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
@@ -4838,13 +4853,13 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>80</v>
@@ -4852,10 +4867,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4878,16 +4893,16 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4913,31 +4928,31 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="Z25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4961,13 +4976,13 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>80</v>
@@ -4975,10 +4990,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5001,13 +5016,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5058,7 +5073,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5079,16 +5094,16 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>80</v>
@@ -5096,10 +5111,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5122,13 +5137,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5179,7 +5194,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5203,24 +5218,24 @@
         <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5243,13 +5258,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5300,7 +5315,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5327,7 +5342,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5338,10 +5353,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5370,7 +5385,7 @@
         <v>138</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>140</v>
@@ -5411,19 +5426,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5450,7 +5465,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5461,10 +5476,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5487,16 +5502,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5546,7 +5561,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5555,7 +5570,7 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>103</v>
@@ -5584,10 +5599,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5613,13 +5628,13 @@
         <v>105</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5645,13 +5660,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5669,7 +5684,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5707,10 +5722,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5736,13 +5751,13 @@
         <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5792,7 +5807,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5819,7 +5834,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5830,10 +5845,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5856,16 +5871,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5915,7 +5930,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5930,7 +5945,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5953,10 +5968,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5979,13 +5994,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6036,7 +6051,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6051,7 +6066,7 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -6060,24 +6075,24 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6100,13 +6115,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6157,7 +6172,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6181,10 +6196,10 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6195,10 +6210,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6221,13 +6236,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6254,13 +6269,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -6278,7 +6293,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6293,7 +6308,7 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -6302,24 +6317,24 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6342,13 +6357,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6375,13 +6390,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6399,7 +6414,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6423,24 +6438,24 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6463,13 +6478,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6520,7 +6535,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6547,7 +6562,7 @@
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6558,10 +6573,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6590,7 +6605,7 @@
         <v>138</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>140</v>
@@ -6631,19 +6646,19 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6670,7 +6685,7 @@
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6681,10 +6696,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6707,19 +6722,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6768,7 +6783,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6792,10 +6807,10 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6806,10 +6821,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6832,19 +6847,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6893,7 +6908,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6908,7 +6923,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>80</v>
@@ -6917,10 +6932,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6931,10 +6946,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6957,13 +6972,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7014,7 +7029,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7038,10 +7053,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7052,10 +7067,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7078,13 +7093,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7135,7 +7150,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7156,13 +7171,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7173,10 +7188,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7199,13 +7214,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7256,7 +7271,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7283,7 +7298,7 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7294,10 +7309,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7326,7 +7341,7 @@
         <v>138</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>140</v>
@@ -7379,7 +7394,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7406,7 +7421,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7417,14 +7432,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7446,10 +7461,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>140</v>
@@ -7504,7 +7519,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7542,10 +7557,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7568,13 +7583,13 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7601,13 +7616,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7625,7 +7640,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7646,13 +7661,13 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7663,10 +7678,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7689,16 +7704,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7748,7 +7763,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -7769,16 +7784,16 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7786,10 +7801,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7812,13 +7827,13 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7869,7 +7884,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7890,13 +7905,13 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -7907,10 +7922,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7933,13 +7948,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7966,13 +7981,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7990,7 +8005,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8011,13 +8026,13 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8028,10 +8043,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8054,13 +8069,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8111,7 +8126,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8132,7 +8147,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8149,10 +8164,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8175,23 +8190,23 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>80</v>
@@ -8236,7 +8251,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8260,7 +8275,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8274,10 +8289,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8300,13 +8315,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8333,13 +8348,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8357,7 +8372,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8395,10 +8410,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8421,13 +8436,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8478,7 +8493,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8490,7 +8505,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8516,10 +8531,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8542,13 +8557,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8599,7 +8614,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8626,7 +8641,7 @@
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -8637,10 +8652,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8669,7 +8684,7 @@
         <v>138</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>140</v>
@@ -8722,7 +8737,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8749,7 +8764,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8760,14 +8775,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8789,10 +8804,10 @@
         <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -8847,7 +8862,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8885,10 +8900,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8911,13 +8926,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8968,7 +8983,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8992,7 +9007,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>134</v>
@@ -9006,10 +9021,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9035,10 +9050,10 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9089,7 +9104,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9127,10 +9142,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9153,13 +9168,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9210,7 +9225,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9234,7 +9249,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>134</v>
@@ -9248,10 +9263,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9274,13 +9289,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9331,7 +9346,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9355,7 +9370,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>134</v>
@@ -9369,10 +9384,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9395,13 +9410,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9428,13 +9443,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9452,7 +9467,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9476,7 +9491,7 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>134</v>
@@ -9490,10 +9505,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9516,13 +9531,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9549,13 +9564,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9573,7 +9588,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9611,10 +9626,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9637,16 +9652,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9696,7 +9711,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9720,10 +9735,10 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9734,10 +9749,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9760,13 +9775,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9817,7 +9832,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9844,7 +9859,7 @@
         <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9855,10 +9870,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9887,7 +9902,7 @@
         <v>138</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>140</v>
@@ -9940,7 +9955,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9967,7 +9982,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9978,14 +9993,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10007,10 +10022,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>140</v>
@@ -10065,7 +10080,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10103,10 +10118,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10129,13 +10144,13 @@
         <v>80</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10186,7 +10201,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10210,10 +10225,10 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>80</v>
@@ -10224,10 +10239,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10250,13 +10265,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10307,7 +10322,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10331,10 +10346,10 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10345,10 +10360,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10371,13 +10386,13 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10428,7 +10443,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10452,10 +10467,10 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>80</v>
@@ -10466,10 +10481,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10492,13 +10507,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10549,7 +10564,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10587,10 +10602,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10613,13 +10628,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10670,7 +10685,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10697,7 +10712,7 @@
         <v>80</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -10708,10 +10723,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10740,7 +10755,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -10793,7 +10808,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10820,7 +10835,7 @@
         <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>80</v>
@@ -10831,14 +10846,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10860,10 +10875,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -10918,7 +10933,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10956,10 +10971,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10982,13 +10997,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11039,7 +11054,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11077,10 +11092,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11103,13 +11118,13 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11160,7 +11175,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11198,10 +11213,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11224,13 +11239,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11257,13 +11272,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11281,7 +11296,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11319,10 +11334,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11345,16 +11360,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11392,17 +11407,17 @@
         <v>80</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>91</v>
@@ -11440,13 +11455,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="B79" t="s" s="2">
-        <v>482</v>
-      </c>
       <c r="C79" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11468,16 +11483,16 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11527,7 +11542,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>91</v>
@@ -11542,7 +11557,7 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>80</v>
@@ -11565,10 +11580,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11591,16 +11606,16 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11650,7 +11665,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -681,7 +681,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1878: source value from ADERS - 17_Vac1_TypeBrand</t>
+    <t>1878: source value based on ADERS - 17_Vac1_TypeBrand</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -707,7 +707,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>1876: reference from ADERS - 0_Pt_ICN_Full</t>
+    <t>1876: reference based on ADERS - 0_Pt_ICN_Full</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -989,7 +989,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1883: source value from ADERS - 17_Vac1_Mfgr</t>
+    <t>1883: source value based on ADERS - 17_Vac1_Mfgr</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -1001,7 +1001,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1884: source value from ADERS - 17_Vac1_Lot</t>
+    <t>1884: source value based on ADERS - 17_Vac1_Lot</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1047,7 +1047,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1885: source value from ADERS - 17_Vac1_Site</t>
+    <t>1885: source value based on ADERS - 17_Vac1_Site</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1095,7 +1095,7 @@
     <t>Immunization.route.text</t>
   </si>
   <si>
-    <t>1879: source value from ADERS - 17_Vac1_Route</t>
+    <t>1879: source value based on ADERS - 17_Vac1_Route</t>
   </si>
   <si>
     <t>Immunization.doseQuantity</t>
@@ -1543,7 +1543,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1886: source value from ADERS - 17_Vac1_DoseInSeries</t>
+    <t>1886: source value based on ADERS - 17_Vac1_DoseInSeries</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -681,7 +681,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1878: source value based on ADERS - 17_Vac1_TypeBrand</t>
+    <t>1878: source value based on ADERS - 17_Vac1_TypeBrand (17-1.1)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -707,7 +707,7 @@
     <t>The patient who either received or did not receive the immunization.</t>
   </si>
   <si>
-    <t>1876: reference based on ADERS - 0_Pt_ICN_Full</t>
+    <t>1876: reference based on ADERS - 0_Pt_ICN_Full (0)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -989,7 +989,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1883: source value based on ADERS - 17_Vac1_Mfgr</t>
+    <t>1883: source value based on ADERS - 17_Vac1_Mfgr (17-1.2)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -1001,7 +1001,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1884: source value based on ADERS - 17_Vac1_Lot</t>
+    <t>1884: source value based on ADERS - 17_Vac1_Lot (17-1.3)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1047,7 +1047,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1885: source value based on ADERS - 17_Vac1_Site</t>
+    <t>1885: source value based on ADERS - 17_Vac1_Site (17-1.5)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1095,7 +1095,7 @@
     <t>Immunization.route.text</t>
   </si>
   <si>
-    <t>1879: source value based on ADERS - 17_Vac1_Route</t>
+    <t>1879: source value based on ADERS - 17_Vac1_Route (17-1.4)</t>
   </si>
   <si>
     <t>Immunization.doseQuantity</t>
@@ -1543,7 +1543,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1886: source value based on ADERS - 17_Vac1_DoseInSeries</t>
+    <t>1886: source value based on ADERS - 17_Vac1_DoseInSeries (17-1.6)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunizationvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
